--- a/public/sap-reporting/expansion-150-downloads/EXT-MM21-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-MM21-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rf6773158817840c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2194897d21ed4629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R9c62cf9e8f784356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rd49093f4b31745d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R19e2ed49ab3a4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R7ab93650a98240f2"/>
   </x:sheets>
 </x:workbook>
 </file>
